--- a/資料/ゲーム仕様書_4GA3_遠藤直樹_随時更新.xlsx
+++ b/資料/ゲーム仕様書_4GA3_遠藤直樹_随時更新.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Winter\資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91978F91-6D64-47ED-9CDE-843C06B7F94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADB0C4B-D418-451C-91B7-FD21080539F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72F6F5E8-1278-489D-A503-583D3EF5BC33}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{72F6F5E8-1278-489D-A503-583D3EF5BC33}"/>
   </bookViews>
   <sheets>
     <sheet name="企画概要" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="モンスターについて" sheetId="5" r:id="rId5"/>
     <sheet name="マップについて" sheetId="6" r:id="rId6"/>
     <sheet name="タイプ相性について" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
   <si>
     <t>企画概要</t>
     <rPh sb="0" eb="2">
@@ -500,6 +501,10 @@
     <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -13082,4 +13087,20 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4102E979-7672-43EA-A799-95600F9F4560}">
+  <dimension ref="R24"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="24" spans="18:18" x14ac:dyDescent="0.4">
+      <c r="R24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/資料/ゲーム仕様書_4GA3_遠藤直樹_随時更新.xlsx
+++ b/資料/ゲーム仕様書_4GA3_遠藤直樹_随時更新.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Winter\資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026 Winter\資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADB0C4B-D418-451C-91B7-FD21080539F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AB7097-E239-4FCA-A923-070AA6C47CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{72F6F5E8-1278-489D-A503-583D3EF5BC33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72F6F5E8-1278-489D-A503-583D3EF5BC33}"/>
   </bookViews>
   <sheets>
     <sheet name="企画概要" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
   <si>
     <t>企画概要</t>
     <rPh sb="0" eb="2">
@@ -505,6 +508,149 @@
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>地方の名前はリュウシ地方</t>
+    <rPh sb="0" eb="2">
+      <t>チホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太古にいたといわれてる竜が眠っている。</t>
+    <rPh sb="0" eb="2">
+      <t>タイコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その竜を至る所で奉っている</t>
+    <rPh sb="2" eb="3">
+      <t>リュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トコロ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9の町と12の道路がある</t>
+    <rPh sb="2" eb="3">
+      <t>マチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ドウロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>始まりの町　シモウミタウン</t>
+    <rPh sb="0" eb="1">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武士の町</t>
+    <rPh sb="0" eb="2">
+      <t>ブシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛媛</t>
+    <rPh sb="0" eb="2">
+      <t>エヒメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徳島</t>
+    <rPh sb="0" eb="2">
+      <t>トクシマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岡山</t>
+    <rPh sb="0" eb="2">
+      <t>オカヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神話の土地　カミシロタウン</t>
+    <rPh sb="0" eb="2">
+      <t>シンワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>砂の町　</t>
+    <rPh sb="0" eb="1">
+      <t>スナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>都会の街　グランドシティ</t>
+    <rPh sb="0" eb="2">
+      <t>トカイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>海辺の町　</t>
+    <rPh sb="0" eb="2">
+      <t>ウミベ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食の町　</t>
+    <rPh sb="0" eb="1">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -11907,9 +12053,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -11947,7 +12093,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -12053,7 +12199,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12195,7 +12341,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -12436,7 +12582,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2B0CA8-4470-48B3-BF61-F5A2966BC456}">
-  <dimension ref="B2:C2"/>
+  <dimension ref="B2:C16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
@@ -12447,9 +12593,80 @@
         <v>16</v>
       </c>
     </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/資料/ゲーム仕様書_4GA3_遠藤直樹_随時更新.xlsx
+++ b/資料/ゲーム仕様書_4GA3_遠藤直樹_随時更新.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026 Winter\資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AB7097-E239-4FCA-A923-070AA6C47CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B1930C-A27A-4B29-AD05-FA606C3A6E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72F6F5E8-1278-489D-A503-583D3EF5BC33}"/>
+    <workbookView xWindow="5175" yWindow="3600" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{72F6F5E8-1278-489D-A503-583D3EF5BC33}"/>
   </bookViews>
   <sheets>
     <sheet name="企画概要" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="93">
   <si>
     <t>企画概要</t>
     <rPh sb="0" eb="2">
@@ -651,6 +651,166 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>その地方には真の紳士淑女になるために八つの試練が行われている</t>
+    <rPh sb="2" eb="4">
+      <t>チホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>シンシシュクジョ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヤッ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シレン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシステムとしては</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バトルシーンではモンスター同士が一対一でコマンド選択型RPG</t>
+    <rPh sb="13" eb="15">
+      <t>ドウシ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>イチタイイチ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>センタクガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パレス攻略ではその町のNPCなどから教わることができる紳士淑女になるためのマナーなどの質問が行われる</t>
+    <rPh sb="3" eb="5">
+      <t>コウリャク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>シンシシュクジョ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇=効果抜群　威力二倍</t>
+    <rPh sb="2" eb="6">
+      <t>コウカバツグン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>イリョクニバイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空白　等倍</t>
+    <rPh sb="0" eb="2">
+      <t>クウハク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウバイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△=効果いまひとつ　威力半減</t>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>イリョクハンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×=効果なし　無効</t>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ムコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>舞踊の町</t>
+    <rPh sb="0" eb="2">
+      <t>ブヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山口</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマグチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>島根</t>
+    <rPh sb="0" eb="2">
+      <t>シマネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鳥取</t>
+    <rPh sb="0" eb="2">
+      <t>トットリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広島</t>
+    <rPh sb="0" eb="2">
+      <t>ヒロシマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福山</t>
+    <rPh sb="0" eb="2">
+      <t>フクヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>香川</t>
+    <rPh sb="0" eb="2">
+      <t>カガワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高知</t>
+    <rPh sb="0" eb="2">
+      <t>コウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -710,7 +870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -721,6 +881,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12549,6 +12712,21 @@
         <v>38</v>
       </c>
     </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+    </row>
     <row r="22" spans="20:20" x14ac:dyDescent="0.4">
       <c r="T22" t="s">
         <v>22</v>
@@ -12582,7 +12760,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2B0CA8-4470-48B3-BF61-F5A2966BC456}">
-  <dimension ref="B2:C16"/>
+  <dimension ref="B2:C17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
@@ -12610,56 +12788,91 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
       <c r="C16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
         <v>71</v>
       </c>
     </row>
@@ -12672,7 +12885,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A49A763-4429-474D-BCE1-05BA8265DA66}">
-  <dimension ref="A2:T21"/>
+  <dimension ref="A2:T27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="1:20" x14ac:dyDescent="0.4">
@@ -13300,6 +13513,26 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
     </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B24" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B25" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B26" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.4">
+      <c r="B27" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
